--- a/poker/resources/sample/poolResults.xlsx
+++ b/poker/resources/sample/poolResults.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14160" windowHeight="7485"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="poolResults" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,21 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>输赢的局数：游戏倍数_修改权重|游戏倍数_修改权重|.....
+输赢的局数说明：负数代表连输多少局，正数代表连赢多少局；
+游戏倍数说明：牌型倍数；
+修改权重：在typeProp字段中的倍数权重基础上继续修改，+代表在原先的权重上增加，-代表在原先的权重上减少；</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
@@ -394,12 +409,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -895,6 +910,9 @@
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1334,7 +1352,7 @@
       <c r="E5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="16" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="12">

--- a/poker/resources/sample/poolResults.xlsx
+++ b/poker/resources/sample/poolResults.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="14160" windowHeight="7485"/>
   </bookViews>
   <sheets>
     <sheet name="poolResults" sheetId="1" r:id="rId1"/>
@@ -33,21 +33,6 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>输赢的局数：游戏倍数_修改权重|游戏倍数_修改权重|.....
-输赢的局数说明：负数代表连输多少局，正数代表连赢多少局；
-游戏倍数说明：牌型倍数；
-修改权重：在typeProp字段中的倍数权重基础上继续修改，+代表在原先的权重上增加，-代表在原先的权重上减少；</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
@@ -409,12 +394,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -910,9 +895,6 @@
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1352,7 +1334,7 @@
       <c r="E5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="12">

--- a/poker/resources/sample/poolResults.xlsx
+++ b/poker/resources/sample/poolResults.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t>92%-94%</t>
+  </si>
+  <si>
+    <t>南方前进-体验场</t>
   </si>
   <si>
     <t>体验优化法（平滑）</t>
@@ -409,12 +412,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1560,8 +1563,229 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="8"/>
+    <row r="12" ht="16.5" spans="1:10">
+      <c r="A12" s="8">
+        <v>4008</v>
+      </c>
+      <c r="B12" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="12">
+        <v>8000</v>
+      </c>
+      <c r="H12" s="12">
+        <v>999999</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:10">
+      <c r="A13" s="8">
+        <v>4009</v>
+      </c>
+      <c r="B13" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="10">
+        <v>2</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="12">
+        <v>6000</v>
+      </c>
+      <c r="H13" s="12">
+        <v>8000</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:10">
+      <c r="A14" s="8">
+        <v>4010</v>
+      </c>
+      <c r="B14" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="10">
+        <v>3</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="12">
+        <v>4000</v>
+      </c>
+      <c r="H14" s="12">
+        <v>6000</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.985</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:10">
+      <c r="A15" s="8">
+        <v>4011</v>
+      </c>
+      <c r="B15" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="10">
+        <v>4</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="12">
+        <v>2000</v>
+      </c>
+      <c r="H15" s="12">
+        <v>4000</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="14">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:10">
+      <c r="A16" s="8">
+        <v>4012</v>
+      </c>
+      <c r="B16" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="10">
+        <v>5</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>2000</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:10">
+      <c r="A17" s="8">
+        <v>4013</v>
+      </c>
+      <c r="B17" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="10">
+        <v>6</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="12">
+        <v>-1000</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:10">
+      <c r="A18" s="8">
+        <v>4014</v>
+      </c>
+      <c r="B18" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="10">
+        <v>7</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="12">
+        <v>-999999</v>
+      </c>
+      <c r="H18" s="12">
+        <v>-1000</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="17.25" spans="5:6">
       <c r="E37" s="2"/>
@@ -1606,18 +1830,18 @@
     <row r="13" ht="27" customHeight="1"/>
     <row r="14" ht="17.25" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="17.25" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/poolResults.xlsx
+++ b/poker/resources/sample/poolResults.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14160" windowHeight="7485"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="poolResults" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,21 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>输赢的局数：游戏倍数_修改权重|游戏倍数_修改权重|.....
+输赢的局数说明：负数代表连输多少局，正数代表连赢多少局；
+游戏倍数说明：牌型倍数；
+修改权重：在typeProp字段中的倍数权重基础上继续修改，+代表在原先的权重上增加，-代表在原先的权重上减少；</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
@@ -97,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -205,6 +220,9 @@
   </si>
   <si>
     <t>92%-94%</t>
+  </si>
+  <si>
+    <t>南方前进-体验场</t>
   </si>
   <si>
     <t>体验优化法（平滑）</t>
@@ -895,6 +913,9 @@
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1334,7 +1355,7 @@
       <c r="E5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="16" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="12">
@@ -1542,8 +1563,229 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="8"/>
+    <row r="12" ht="16.5" spans="1:10">
+      <c r="A12" s="8">
+        <v>4008</v>
+      </c>
+      <c r="B12" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="12">
+        <v>8000</v>
+      </c>
+      <c r="H12" s="12">
+        <v>999999</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:10">
+      <c r="A13" s="8">
+        <v>4009</v>
+      </c>
+      <c r="B13" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="10">
+        <v>2</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="12">
+        <v>6000</v>
+      </c>
+      <c r="H13" s="12">
+        <v>8000</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:10">
+      <c r="A14" s="8">
+        <v>4010</v>
+      </c>
+      <c r="B14" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="10">
+        <v>3</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="12">
+        <v>4000</v>
+      </c>
+      <c r="H14" s="12">
+        <v>6000</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.985</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:10">
+      <c r="A15" s="8">
+        <v>4011</v>
+      </c>
+      <c r="B15" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="10">
+        <v>4</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="12">
+        <v>2000</v>
+      </c>
+      <c r="H15" s="12">
+        <v>4000</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="14">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:10">
+      <c r="A16" s="8">
+        <v>4012</v>
+      </c>
+      <c r="B16" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="10">
+        <v>5</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>2000</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:10">
+      <c r="A17" s="8">
+        <v>4013</v>
+      </c>
+      <c r="B17" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="10">
+        <v>6</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="12">
+        <v>-1000</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:10">
+      <c r="A18" s="8">
+        <v>4014</v>
+      </c>
+      <c r="B18" s="8">
+        <v>300402</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="10">
+        <v>7</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="12">
+        <v>-999999</v>
+      </c>
+      <c r="H18" s="12">
+        <v>-1000</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="17.25" spans="5:6">
       <c r="E37" s="2"/>
@@ -1588,18 +1830,18 @@
     <row r="13" ht="27" customHeight="1"/>
     <row r="14" ht="17.25" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="17.25" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/poolResults.xlsx
+++ b/poker/resources/sample/poolResults.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
   <si>
     <t>id</t>
   </si>
@@ -138,6 +138,9 @@
     <t>对应水池描述</t>
   </si>
   <si>
+    <t>总权重</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -223,6 +226,27 @@
   </si>
   <si>
     <t>南方前进-体验场</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:1|-26:2|-19:2|-13:2|-6:40|0:120|6:80|13:140|19:100|26:80|32:80|39:130|45:120|52:110|58:90|65:70|72:50|78:30|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:1|-26:2|-19:3|-13:4|-6:50|0:200|6:100|13:150|19:100|26:80|32:70|39:90|45:80|52:70|58:55|65:45|72:35|78:25|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:5|-26:5|-19:5|-13:5|-6:100|0:200|6:200|13:120|19:80|26:60|32:40|39:55|45:45|52:45|58:40|65:35|72:20|78:10|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:6|-26:10|-19:12|-13:12|-6:120|0:250|6:200|13:110|19:60|26:40|32:40|39:40|45:30|52:25|58:23|65:17|72:10|78:5|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:5|-26:10|-19:20|-13:25|-6:150|0:200|6:200|13:80|19:50|26:40|32:30|39:25|45:25|52:20|58:10|65:10|72:6|78:4|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:5|-26:15|-19:25|-13:35|-6:180|0:200|6:150|13:60|19:40|26:30|32:20|39:15|45:10|52:8|58:7|65:5|72:3|78:2|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:10|-26:20|-19:30|-13:40|-6:200|0:150|6:150|13:40|19:30|26:20|32:10|39:5|45:3|52:3|58:3|65:3|72:2|78:1|99999:0</t>
   </si>
   <si>
     <t>体验优化法（平滑）</t>
@@ -412,12 +436,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1237,7 +1261,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -1251,7 +1275,7 @@
     <col min="10" max="10" width="16.7833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" ht="16.5" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1277,58 +1301,61 @@
       <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:10">
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:11">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" ht="16.5" spans="1:10">
+    <row r="3" ht="16.5" spans="1:11">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" ht="16.5" spans="1:10">
+    <row r="4" ht="16.5" spans="1:11">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1339,7 +1366,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
+    <row r="5" ht="16.5" spans="1:11">
       <c r="A5" s="8">
         <v>4001</v>
       </c>
@@ -1347,16 +1374,16 @@
         <v>300400</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="10">
         <v>1</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="12">
         <v>8000</v>
@@ -1365,13 +1392,13 @@
         <v>999999</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="8">
         <v>4002</v>
       </c>
@@ -1379,16 +1406,16 @@
         <v>300400</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="10">
         <v>2</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="12">
         <v>6000</v>
@@ -1397,13 +1424,13 @@
         <v>8000</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J6" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:10">
+    <row r="7" ht="16.5" spans="1:11">
       <c r="A7" s="8">
         <v>4003</v>
       </c>
@@ -1411,16 +1438,16 @@
         <v>300400</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="10">
         <v>3</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" s="12">
         <v>4000</v>
@@ -1429,13 +1456,13 @@
         <v>6000</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7" s="15">
         <v>0.985</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:10">
+    <row r="8" ht="16.5" spans="1:11">
       <c r="A8" s="8">
         <v>4004</v>
       </c>
@@ -1443,16 +1470,16 @@
         <v>300400</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="10">
         <v>4</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" s="12">
         <v>2000</v>
@@ -1461,13 +1488,13 @@
         <v>4000</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J8" s="14">
         <v>0.97</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:10">
+    <row r="9" ht="16.5" spans="1:11">
       <c r="A9" s="8">
         <v>4005</v>
       </c>
@@ -1475,16 +1502,16 @@
         <v>300400</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="10">
         <v>5</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="12">
         <v>0</v>
@@ -1493,13 +1520,13 @@
         <v>2000</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J9" s="14">
         <v>0.96</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:10">
+    <row r="10" ht="16.5" spans="1:11">
       <c r="A10" s="8">
         <v>4006</v>
       </c>
@@ -1507,16 +1534,16 @@
         <v>300400</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" s="10">
         <v>6</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" s="12">
         <v>-1000</v>
@@ -1525,13 +1552,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:11">
       <c r="A11" s="8">
         <v>4007</v>
       </c>
@@ -1539,16 +1566,16 @@
         <v>300400</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="10">
         <v>7</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" s="12">
         <v>-999999</v>
@@ -1557,13 +1584,13 @@
         <v>-1000</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:10">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:11">
       <c r="A12" s="8">
         <v>4008</v>
       </c>
@@ -1571,16 +1598,16 @@
         <v>300402</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" s="10">
         <v>1</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G12" s="12">
         <v>8000</v>
@@ -1589,13 +1616,16 @@
         <v>999999</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:10">
+      <c r="J12" s="15">
+        <v>1.3363</v>
+      </c>
+      <c r="K12">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:11">
       <c r="A13" s="8">
         <v>4009</v>
       </c>
@@ -1603,16 +1633,16 @@
         <v>300402</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="10">
         <v>2</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="G13" s="12">
         <v>6000</v>
@@ -1621,13 +1651,16 @@
         <v>8000</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="J13" s="15">
+        <v>1.2698</v>
+      </c>
+      <c r="K13">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:11">
       <c r="A14" s="8">
         <v>4010</v>
       </c>
@@ -1635,16 +1668,16 @@
         <v>300402</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" s="10">
         <v>3</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>40</v>
       </c>
       <c r="G14" s="12">
         <v>4000</v>
@@ -1653,13 +1686,16 @@
         <v>6000</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J14" s="15">
-        <v>0.985</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:10">
+        <v>1.2058</v>
+      </c>
+      <c r="K14">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:11">
       <c r="A15" s="8">
         <v>4011</v>
       </c>
@@ -1667,16 +1703,16 @@
         <v>300402</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="10">
         <v>4</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>26</v>
+        <v>19</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>41</v>
       </c>
       <c r="G15" s="12">
         <v>2000</v>
@@ -1685,13 +1721,16 @@
         <v>4000</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="14">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:10">
+        <v>28</v>
+      </c>
+      <c r="J15" s="15">
+        <v>1.1496</v>
+      </c>
+      <c r="K15">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:11">
       <c r="A16" s="8">
         <v>4012</v>
       </c>
@@ -1699,16 +1738,16 @@
         <v>300402</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="10">
         <v>5</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>28</v>
+        <v>19</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>42</v>
       </c>
       <c r="G16" s="12">
         <v>0</v>
@@ -1717,13 +1756,16 @@
         <v>2000</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="14">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:10">
+        <v>30</v>
+      </c>
+      <c r="J16" s="15">
+        <v>1.1194</v>
+      </c>
+      <c r="K16">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:11">
       <c r="A17" s="8">
         <v>4013</v>
       </c>
@@ -1731,16 +1773,16 @@
         <v>300402</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="10">
         <v>6</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>30</v>
+        <v>19</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="G17" s="12">
         <v>-1000</v>
@@ -1749,13 +1791,16 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:10">
+      <c r="J17" s="15">
+        <v>1.0773</v>
+      </c>
+      <c r="K17">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:11">
       <c r="A18" s="8">
         <v>4014</v>
       </c>
@@ -1763,16 +1808,16 @@
         <v>300402</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" s="10">
         <v>7</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>33</v>
+        <v>19</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="G18" s="12">
         <v>-999999</v>
@@ -1781,10 +1826,13 @@
         <v>-1000</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" s="13" t="s">
         <v>35</v>
+      </c>
+      <c r="J18" s="15">
+        <v>1.0415</v>
+      </c>
+      <c r="K18">
+        <v>720</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="17.25" spans="5:6">
@@ -1830,18 +1878,18 @@
     <row r="13" ht="27" customHeight="1"/>
     <row r="14" ht="17.25" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" ht="17.25" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/poolResults.xlsx
+++ b/poker/resources/sample/poolResults.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\chess\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -112,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="59">
   <si>
     <t>id</t>
   </si>
@@ -247,6 +252,36 @@
   </si>
   <si>
     <t>-99999:0|-32:10|-26:20|-19:30|-13:40|-6:200|0:150|6:150|13:40|19:30|26:20|32:10|39:5|45:3|52:3|58:3|65:3|72:2|78:1|99999:0</t>
+  </si>
+  <si>
+    <t>斗仙牌</t>
+  </si>
+  <si>
+    <t>-5:-99999_0|-1600_70|-800_80|-400_90|-200_100|-50_110|0_120|50_130|200_150|400_170|800_190|1600_210|99999_0;5:-99999_0|-1600_210|-800_190|-400_170|-200_150|-50_130|0_120|50_110|200_100|400_90|800_80|1600_70|99999_0</t>
+  </si>
+  <si>
+    <t>-99999:0|-1600:5|-800:10|-400:20|-200:40|-50:70|0:100|50:130|200:180|400:230|800:280|1600:340|99999:0</t>
+  </si>
+  <si>
+    <t>首轮32张；后续随机8次；连输-3/-5/-8</t>
+  </si>
+  <si>
+    <t>-99999:0|-1600:10|-800:20|-400:35|-200:55|-50:80|0:110|50:135|200:170|400:210|800:250|1600:280|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-1600:20|-800:35|-400:50|-200:70|-50:90|0:120|50:135|200:155|400:180|800:200|1600:220|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-1600:50|-800:80|-400:110|-200:140|-50:170|0:200|50:170|200:140|400:110|800:80|1600:50|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-1600:220|-800:200|-400:180|-200:155|-50:135|0:120|50:90|200:70|400:50|800:35|1600:20|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-1600:280|-800:250|-400:210|-200:170|-50:135|0:110|50:80|200:55|400:35|800:20|1600:10|99999:0</t>
+  </si>
+  <si>
+    <t>-99999:0|-1600:340|-800:280|-400:230|-200:180|-50:130|0:100|50:70|200:40|400:20|800:10|1600:5|99999:0</t>
   </si>
   <si>
     <t>体验优化法（平滑）</t>
@@ -271,7 +306,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +324,12 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -764,141 +805,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -938,6 +980,7 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1268,7 +1311,7 @@
     <col min="2" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="99.2916666666667" customWidth="1"/>
-    <col min="6" max="6" width="120.35" style="3" customWidth="1"/>
+    <col min="6" max="6" width="120.35" style="4" customWidth="1"/>
     <col min="7" max="7" width="15.625" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
@@ -1276,29 +1319,29 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="K1" t="s">
@@ -1306,319 +1349,319 @@
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="4"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" ht="16.5" spans="1:11">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <v>4001</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="9">
         <v>300400</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="11">
         <v>1</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <v>8000</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <v>999999</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:11">
-      <c r="A6" s="8">
+      <c r="A6" s="9">
         <v>4002</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <v>300400</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="11">
         <v>2</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="13">
         <v>6000</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="13">
         <v>8000</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:11">
-      <c r="A7" s="8">
+      <c r="A7" s="9">
         <v>4003</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="9">
         <v>300400</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="11">
         <v>3</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <v>4000</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <v>6000</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="16">
         <v>0.985</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:11">
-      <c r="A8" s="8">
+      <c r="A8" s="9">
         <v>4004</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="9">
         <v>300400</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="11">
         <v>4</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <v>2000</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <v>4000</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="15">
         <v>0.97</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:11">
-      <c r="A9" s="8">
+      <c r="A9" s="9">
         <v>4005</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="9">
         <v>300400</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="11">
         <v>5</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="13">
         <v>0</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="13">
         <v>2000</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="15">
         <v>0.96</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:11">
-      <c r="A10" s="8">
+      <c r="A10" s="9">
         <v>4006</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <v>300400</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="11">
         <v>6</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <v>-1000</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <v>0</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:11">
-      <c r="A11" s="8">
+      <c r="A11" s="9">
         <v>4007</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="9">
         <v>300400</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <v>7</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <v>-999999</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <v>-1000</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:11">
-      <c r="A12" s="8">
+      <c r="A12" s="9">
         <v>4008</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="9">
         <v>300402</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="11">
         <v>1</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <v>8000</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="13">
         <v>999999</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="16">
         <v>1.3363</v>
       </c>
       <c r="K12">
@@ -1626,34 +1669,34 @@
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:11">
-      <c r="A13" s="8">
+      <c r="A13" s="9">
         <v>4009</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <v>300402</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <v>2</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <v>6000</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <v>8000</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="16">
         <v>1.2698</v>
       </c>
       <c r="K13">
@@ -1661,34 +1704,34 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:11">
-      <c r="A14" s="8">
+      <c r="A14" s="9">
         <v>4010</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="9">
         <v>300402</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="11">
         <v>3</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <v>4000</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <v>6000</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="16">
         <v>1.2058</v>
       </c>
       <c r="K14">
@@ -1696,34 +1739,34 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:11">
-      <c r="A15" s="8">
+      <c r="A15" s="9">
         <v>4011</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <v>300402</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="11">
         <v>4</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <v>2000</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <v>4000</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="16">
         <v>1.1496</v>
       </c>
       <c r="K15">
@@ -1731,34 +1774,34 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:11">
-      <c r="A16" s="8">
+      <c r="A16" s="9">
         <v>4012</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="9">
         <v>300402</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="11">
         <v>5</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <v>0</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <v>2000</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="16">
         <v>1.1194</v>
       </c>
       <c r="K16">
@@ -1766,34 +1809,34 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:11">
-      <c r="A17" s="8">
+      <c r="A17" s="9">
         <v>4013</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="9">
         <v>300402</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="11">
         <v>6</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="13">
         <v>-1000</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <v>0</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="16">
         <v>1.0773</v>
       </c>
       <c r="K17">
@@ -1801,66 +1844,311 @@
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:11">
-      <c r="A18" s="8">
+      <c r="A18" s="9">
         <v>4014</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="9">
         <v>300402</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="11">
         <v>7</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <v>-999999</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <v>-1000</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="16">
         <v>1.0415</v>
       </c>
       <c r="K18">
         <v>720</v>
       </c>
     </row>
+    <row r="19" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A19" s="3">
+        <v>8001</v>
+      </c>
+      <c r="B19" s="3">
+        <v>300800</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="11">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="13">
+        <v>2000</v>
+      </c>
+      <c r="H19" s="13">
+        <v>999999</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="13">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A20" s="3">
+        <v>8002</v>
+      </c>
+      <c r="B20" s="3">
+        <v>300800</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="11">
+        <v>2</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="13">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="13">
+        <v>2000</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" s="13">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A21" s="3">
+        <v>8003</v>
+      </c>
+      <c r="B21" s="3">
+        <v>300800</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="11">
+        <v>3</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="13">
+        <v>300</v>
+      </c>
+      <c r="H21" s="13">
+        <v>1000</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="13">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A22" s="3">
+        <v>8004</v>
+      </c>
+      <c r="B22" s="3">
+        <v>300800</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="11">
+        <v>4</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="13">
+        <v>-300</v>
+      </c>
+      <c r="H22" s="13">
+        <v>300</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K22" s="13">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A23" s="3">
+        <v>8005</v>
+      </c>
+      <c r="B23" s="3">
+        <v>300800</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="11">
+        <v>5</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="13">
+        <v>-1000</v>
+      </c>
+      <c r="H23" s="13">
+        <v>-300</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" s="13">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A24" s="3">
+        <v>8006</v>
+      </c>
+      <c r="B24" s="3">
+        <v>300800</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="11">
+        <v>6</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="13">
+        <v>-2000</v>
+      </c>
+      <c r="H24" s="13">
+        <v>-1000</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K24" s="13">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="25" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A25" s="3">
+        <v>8007</v>
+      </c>
+      <c r="B25" s="3">
+        <v>300800</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="11">
+        <v>7</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" s="13">
+        <v>-999999</v>
+      </c>
+      <c r="H25" s="13">
+        <v>-2000</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="13">
+        <v>1405</v>
+      </c>
+    </row>
     <row r="37" s="1" customFormat="1" ht="17.25" spans="5:6">
       <c r="E37" s="2"/>
-      <c r="F37" s="13"/>
+      <c r="F37" s="14"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="17.25" spans="5:6">
       <c r="E38" s="2"/>
-      <c r="F38" s="13"/>
+      <c r="F38" s="14"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="17.25" spans="5:6">
       <c r="E39" s="2"/>
-      <c r="F39" s="13"/>
+      <c r="F39" s="14"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="16.5" spans="5:6">
-      <c r="F40" s="13"/>
+      <c r="F40" s="14"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="16.5" spans="5:6">
-      <c r="F41" s="13"/>
+      <c r="F41" s="14"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="16.5" spans="5:6">
-      <c r="F42" s="13"/>
+      <c r="F42" s="14"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="16.5" spans="5:6">
-      <c r="F43" s="13"/>
+      <c r="F43" s="14"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="16.5" spans="5:6">
-      <c r="F44" s="13"/>
+      <c r="F44" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1878,18 +2166,18 @@
     <row r="13" ht="27" customHeight="1"/>
     <row r="14" ht="17.25" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" ht="17.25" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
